--- a/output/pdf_financials_xlsx/UUU.xlsx
+++ b/output/pdf_financials_xlsx/UUU.xlsx
@@ -2199,16 +2199,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.702368</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>6.284766</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.295276</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>7.277691</v>
       </c>
     </row>
     <row r="93">
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.129095</v>
+        <v>-1.697249</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.920372</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>4.893208</v>
@@ -3746,7 +3746,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -3814,7 +3818,11 @@
           <t>Warrants reserve 11, 13</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4320,7 +4328,11 @@
           <t>Share-based payment reserve 8,9</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.810689</v>
       </c>
@@ -4390,7 +4402,11 @@
           <t>Warrants reserve 8,10</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>4.891679</v>
       </c>
@@ -6114,7 +6130,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>-1.826344</v>
       </c>

--- a/output/pdf_financials_xlsx/UUU.xlsx
+++ b/output/pdf_financials_xlsx/UUU.xlsx
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.405713</v>
+        <v>6.336006</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.009139</v>
+        <v>10.208097</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.44452</v>
+        <v>6.013058</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.840832</v>
+        <v>3.657894</v>
       </c>
     </row>
     <row r="11">
@@ -620,16 +620,16 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-1.405713</v>
+        <v>-6.336006</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.009139</v>
+        <v>-10.208097</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.44452</v>
+        <v>-6.013058</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.840832</v>
+        <v>-3.657894</v>
       </c>
     </row>
     <row r="12">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.280254</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.364631</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002968</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.222596</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.280254</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.364631</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.0334</v>
+        <v>0.036368</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.232596</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.35803</v>
+        <v>1.077776</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.5245919999999999</v>
+        <v>0.159961</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.461597</v>
+        <v>0.458629</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.885336</v>
+        <v>0.66274</v>
       </c>
     </row>
     <row r="49">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3426,7 +3426,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.01</v>
       </c>
@@ -5216,7 +5220,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>-0.01</v>
       </c>
@@ -7176,7 +7184,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7290,7 +7298,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -8670,7 +8678,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">

--- a/output/pdf_financials_xlsx/UUU.xlsx
+++ b/output/pdf_financials_xlsx/UUU.xlsx
@@ -2728,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>3.106484</v>
       </c>
     </row>
     <row r="121">
@@ -5438,7 +5438,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/UUU.xlsx
+++ b/output/pdf_financials_xlsx/UUU.xlsx
@@ -1655,16 +1655,16 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.449285</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.156579</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.087877</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.225189</v>
       </c>
     </row>
     <row r="65">
@@ -1712,16 +1712,16 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.008135</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.018275</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.089585</v>
       </c>
     </row>
     <row r="68">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.110974</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.044251</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -2453,10 +2453,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.602774</v>
+        <v>-0.713748</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.957082</v>
+        <v>0.9128309999999999</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.40106</v>
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.043494</v>
       </c>
     </row>
     <row r="116">
@@ -5148,7 +5148,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6070,7 +6074,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>-0.110974</v>
       </c>
